--- a/excel/06数据透视表.xlsx
+++ b/excel/06数据透视表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/cli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zimu/Documents/data-analytics/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96FE5DB0-575C-DB4D-82EC-308D35E28CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B794AD-3852-EB40-AAE5-8E393E71F67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXCEL课件" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId14"/>
+    <pivotCache cacheId="11" r:id="rId14"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -6041,7 +6041,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -6134,20 +6134,26 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" pivotButton="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" pivotButton="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{DFD18E78-EC68-8D47-B3DB-515C0AF631F9}"/>
     <cellStyle name="常规 3" xfId="2" xr:uid="{0E1421C4-67DE-824C-80B5-AA77E3C89151}"/>
   </cellStyles>
-  <dxfs count="301">
+  <dxfs count="195">
     <dxf>
       <font>
         <color theme="0"/>
@@ -6161,14 +6167,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="4"/>
+          <bgColor theme="3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="4"/>
+          <bgColor theme="3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6184,667 +6197,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
       </font>
     </dxf>
     <dxf>
@@ -6875,14 +6228,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="4"/>
+          <bgColor theme="3"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="4"/>
+          <bgColor theme="3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6894,6 +6254,26 @@
     <dxf>
       <font>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
       </font>
     </dxf>
     <dxf>
@@ -7825,6 +7205,50 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -8279,6 +7703,104 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="13"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="14"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="15"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="16"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -8312,6 +7834,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-91D6-184E-B71A-92085ABF477D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -8327,6 +7854,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-91D6-184E-B71A-92085ABF477D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -8342,6 +7874,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-91D6-184E-B71A-92085ABF477D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -8359,6 +7896,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-91D6-184E-B71A-92085ABF477D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -8376,6 +7918,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-91D6-184E-B71A-92085ABF477D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -8393,6 +7940,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-91D6-184E-B71A-92085ABF477D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -8411,6 +7963,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-91D6-184E-B71A-92085ABF477D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -9222,6 +8779,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -9250,6 +8810,9 @@
       <c:pivotFmt>
         <c:idx val="2"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -9278,6 +8841,9 @@
       <c:pivotFmt>
         <c:idx val="3"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -9306,6 +8872,9 @@
       <c:pivotFmt>
         <c:idx val="4"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -9334,6 +8903,9 @@
       <c:pivotFmt>
         <c:idx val="5"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -9362,6 +8934,9 @@
       <c:pivotFmt>
         <c:idx val="6"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -11446,8 +11021,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>169333</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="2" name="部门">
@@ -11470,7 +11045,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -31798,7 +31373,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F854ADEC-1A09-DB44-AB92-4F5C8347D894}" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F854ADEC-1A09-DB44-AB92-4F5C8347D894}" name="数据透视表1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:E11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -32440,10 +32015,10 @@
     <dataField name="总价占比" fld="5" showDataAs="percentOfTotal" baseField="5" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="300">
+    <format dxfId="186">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="299">
+    <format dxfId="185">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -32455,10 +32030,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="298">
+    <format dxfId="184">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="297">
+    <format dxfId="183">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -32470,10 +32045,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="296">
+    <format dxfId="182">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="295">
+    <format dxfId="181">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -32485,7 +32060,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="294">
+    <format dxfId="180">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
   </formats>
@@ -32502,7 +32077,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A147CA3E-0CA1-0541-9E07-FA554A4F3C87}" name="数据透视表10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A147CA3E-0CA1-0541-9E07-FA554A4F3C87}" name="数据透视表10" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="A9:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0"/>
@@ -33117,32 +32692,32 @@
     <dataField name="求和项:总价" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="135">
+    <format dxfId="194">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="134">
+    <format dxfId="193">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="133">
+    <format dxfId="192">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="132">
+    <format dxfId="191">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="131">
+    <format dxfId="190">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="130">
+    <format dxfId="189">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="129">
+    <format dxfId="188">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="128">
+    <format dxfId="187">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
-  <chartFormats count="29">
+  <chartFormats count="36">
     <chartFormat chart="2" format="3" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -33479,6 +33054,90 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="2" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="16">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="1" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -33493,7 +33152,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E32BEFE8-1BD9-964F-B278-70BD1C208BDB}" name="数据透视表2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E32BEFE8-1BD9-964F-B278-70BD1C208BDB}" name="数据透视表2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:K13" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0">
@@ -34965,52 +34624,52 @@
     <dataField name="求和项:总价" fld="5" showDataAs="percentOfRow" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="293">
+    <format dxfId="179">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="292">
+    <format dxfId="178">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="291">
+    <format dxfId="177">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="290">
+    <format dxfId="176">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="289">
+    <format dxfId="175">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="288">
+    <format dxfId="174">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="287">
+    <format dxfId="173">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="286">
+    <format dxfId="172">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="285">
+    <format dxfId="171">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="284">
+    <format dxfId="170">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="283">
+    <format dxfId="169">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="282">
+    <format dxfId="168">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -35033,7 +34692,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5BE86E66-6499-6B4B-BE8E-B410E17E251E}" name="数据透视表3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5BE86E66-6499-6B4B-BE8E-B410E17E251E}" name="数据透视表3" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:K9" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0">
@@ -36489,52 +36148,52 @@
     <dataField name="求和项:总价" fld="5" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="281">
+    <format dxfId="167">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="280">
+    <format dxfId="166">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="279">
+    <format dxfId="165">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="278">
+    <format dxfId="164">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="277">
+    <format dxfId="163">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="276">
+    <format dxfId="162">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="275">
+    <format dxfId="161">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="274">
+    <format dxfId="160">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="273">
+    <format dxfId="159">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="272">
+    <format dxfId="158">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="271">
+    <format dxfId="157">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="270">
+    <format dxfId="156">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -36557,7 +36216,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D4C5665-7833-D64D-A40D-B5874C6B996B}" name="数据透视表4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6D4C5665-7833-D64D-A40D-B5874C6B996B}" name="数据透视表4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:E63" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -37398,19 +37057,19 @@
     </dataField>
   </dataFields>
   <formats count="10">
-    <format dxfId="269">
+    <format dxfId="155">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="268">
+    <format dxfId="154">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="267">
+    <format dxfId="153">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="266">
+    <format dxfId="152">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="265">
+    <format dxfId="151">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -37420,16 +37079,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="264">
+    <format dxfId="150">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="263">
+    <format dxfId="149">
       <pivotArea field="9" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="262">
+    <format dxfId="148">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="261">
+    <format dxfId="147">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -37439,7 +37098,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="260">
+    <format dxfId="146">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -37462,7 +37121,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB93A9D8-021F-4A4D-A790-6ACE76931D23}" name="数据透视表5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB93A9D8-021F-4A4D-A790-6ACE76931D23}" name="数据透视表5" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:R10" firstHeaderRow="1" firstDataRow="4" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0"/>
@@ -38127,42 +37786,42 @@
     <dataField name="求和项:总价" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="76">
-    <format dxfId="259">
+    <format dxfId="145">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="2"/>
     </format>
-    <format dxfId="258">
+    <format dxfId="144">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="257">
+    <format dxfId="143">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="256">
+    <format dxfId="142">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="2"/>
     </format>
-    <format dxfId="255">
+    <format dxfId="141">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="254">
+    <format dxfId="140">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="253">
+    <format dxfId="139">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="252">
+    <format dxfId="138">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0" defaultSubtotal="1"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="251">
+    <format dxfId="137">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="250">
+    <format dxfId="136">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38172,7 +37831,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="249">
+    <format dxfId="135">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38182,7 +37841,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="248">
+    <format dxfId="134">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38192,7 +37851,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="247">
+    <format dxfId="133">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38202,7 +37861,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="246">
+    <format dxfId="132">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38212,7 +37871,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="245">
+    <format dxfId="131">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38222,7 +37881,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="244">
+    <format dxfId="130">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38232,39 +37891,39 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="243">
+    <format dxfId="129">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="242">
+    <format dxfId="128">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="241">
+    <format dxfId="127">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="2"/>
     </format>
-    <format dxfId="240">
+    <format dxfId="126">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="239">
+    <format dxfId="125">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="238">
+    <format dxfId="124">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="237">
+    <format dxfId="123">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0" defaultSubtotal="1"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="236">
+    <format dxfId="122">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="235">
+    <format dxfId="121">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38274,7 +37933,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="234">
+    <format dxfId="120">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38284,7 +37943,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="233">
+    <format dxfId="119">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38294,7 +37953,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="232">
+    <format dxfId="118">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38304,7 +37963,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="231">
+    <format dxfId="117">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38314,7 +37973,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="230">
+    <format dxfId="116">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38324,7 +37983,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="229">
+    <format dxfId="115">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38334,39 +37993,39 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="228">
+    <format dxfId="114">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="227">
+    <format dxfId="113">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="226">
+    <format dxfId="112">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="2"/>
     </format>
-    <format dxfId="225">
+    <format dxfId="111">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="224">
+    <format dxfId="110">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="223">
+    <format dxfId="109">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="222">
+    <format dxfId="108">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0" defaultSubtotal="1"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="221">
+    <format dxfId="107">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="220">
+    <format dxfId="106">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38376,7 +38035,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="219">
+    <format dxfId="105">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38386,7 +38045,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="218">
+    <format dxfId="104">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38396,7 +38055,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="217">
+    <format dxfId="103">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38406,7 +38065,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="216">
+    <format dxfId="102">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38416,7 +38075,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="215">
+    <format dxfId="101">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38426,7 +38085,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="214">
+    <format dxfId="100">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38436,39 +38095,39 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="213">
+    <format dxfId="99">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="212">
+    <format dxfId="98">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="211">
+    <format dxfId="97">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="2"/>
     </format>
-    <format dxfId="210">
+    <format dxfId="96">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="209">
+    <format dxfId="95">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="208">
+    <format dxfId="94">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="207">
+    <format dxfId="93">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0" defaultSubtotal="1"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="206">
+    <format dxfId="92">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="205">
+    <format dxfId="91">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38478,7 +38137,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="204">
+    <format dxfId="90">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38488,7 +38147,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="203">
+    <format dxfId="89">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38498,7 +38157,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="202">
+    <format dxfId="88">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38508,7 +38167,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="201">
+    <format dxfId="87">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38518,7 +38177,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="200">
+    <format dxfId="86">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38528,7 +38187,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="199">
+    <format dxfId="85">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38538,33 +38197,33 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="198">
+    <format dxfId="84">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="197">
+    <format dxfId="83">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="2"/>
     </format>
-    <format dxfId="196">
+    <format dxfId="82">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="195">
+    <format dxfId="81">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="194">
+    <format dxfId="80">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0" defaultSubtotal="1"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="193">
+    <format dxfId="79">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="192">
+    <format dxfId="78">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38574,7 +38233,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="191">
+    <format dxfId="77">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38584,7 +38243,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="190">
+    <format dxfId="76">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38594,7 +38253,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="189">
+    <format dxfId="75">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38604,7 +38263,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="188">
+    <format dxfId="74">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38614,7 +38273,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="187">
+    <format dxfId="73">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38624,7 +38283,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="186">
+    <format dxfId="72">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="1" count="1" selected="0">
@@ -38634,10 +38293,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="185">
+    <format dxfId="71">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="184">
+    <format dxfId="70">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
   </formats>
@@ -38654,7 +38313,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9B5386D-A6A7-C545-BE01-820789EFDC54}" name="数据透视表6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E9B5386D-A6A7-C545-BE01-820789EFDC54}" name="数据透视表6" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:J11" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -39265,43 +38924,43 @@
     <dataField name="求和项:总价" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="183">
+    <format dxfId="69">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="182">
+    <format dxfId="68">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="1"/>
     </format>
-    <format dxfId="181">
+    <format dxfId="67">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="180">
+    <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="179">
+    <format dxfId="65">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="178">
+    <format dxfId="64">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="177">
+    <format dxfId="63">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="176">
+    <format dxfId="62">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="175">
+    <format dxfId="61">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -39318,7 +38977,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7830F17-6FFB-9D40-A99A-6894FFDF9610}" name="数据透视表7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7830F17-6FFB-9D40-A99A-6894FFDF9610}" name="数据透视表7" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:C14" firstHeaderRow="2" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -39899,25 +39558,25 @@
     <dataField name="求和项:总价" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="7">
-    <format dxfId="174">
+    <format dxfId="60">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="173">
+    <format dxfId="59">
       <pivotArea field="24" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="172">
+    <format dxfId="58">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="171">
+    <format dxfId="57">
       <pivotArea field="24" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="170">
+    <format dxfId="56">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="169">
+    <format dxfId="55">
       <pivotArea field="24" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="168">
+    <format dxfId="54">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
   </formats>
@@ -39934,7 +39593,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AAF0B39A-870E-B74E-B34E-17124BB3D7A0}" name="数据透视表8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AAF0B39A-870E-B74E-B34E-17124BB3D7A0}" name="数据透视表8" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:J13" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="25">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -40575,79 +40234,79 @@
     <dataField name="求和项:总价" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="21">
-    <format dxfId="167">
+    <format dxfId="53">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="166">
+    <format dxfId="52">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="165">
+    <format dxfId="51">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="164">
+    <format dxfId="50">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="163">
+    <format dxfId="49">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="162">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="18" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="161">
+    <format dxfId="47">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="160">
+    <format dxfId="46">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="159">
+    <format dxfId="45">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="158">
+    <format dxfId="44">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="157">
+    <format dxfId="43">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="156">
+    <format dxfId="42">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="155">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="18" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="154">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="153">
+    <format dxfId="39">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="152">
+    <format dxfId="38">
       <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="151">
+    <format dxfId="37">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="150">
+    <format dxfId="36">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="149">
+    <format dxfId="35">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="148">
+    <format dxfId="34">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="18" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="147">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -40664,7 +40323,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4A48551F-DAD7-0F41-9403-B49DFB9E7393}" name="数据透视表9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" pageWrap="2" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4A48551F-DAD7-0F41-9403-B49DFB9E7393}" name="数据透视表9" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" pageWrap="2" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A6:D11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="2"/>
   <pivotFields count="25">
     <pivotField showAll="0"/>
@@ -41302,16 +40961,16 @@
     <dataField name="求和项:总价" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="146">
+    <format dxfId="32">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="145">
+    <format dxfId="31">
       <pivotArea field="23" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="144">
+    <format dxfId="30">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="143">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="23" count="2">
@@ -41321,13 +40980,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="142">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="141">
+    <format dxfId="27">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="140">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="23" count="2">
@@ -41337,13 +40996,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="139">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="138">
+    <format dxfId="24">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="137">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="23" count="2">
@@ -41353,7 +41012,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="136">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -42359,7 +42018,7 @@
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="24" width="11" bestFit="1" customWidth="1"/>
     <col min="25" max="31" width="10" bestFit="1" customWidth="1"/>
@@ -42376,30 +42035,30 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="76" t="s">
         <v>1774</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="42" t="s">
         <v>1859</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="76" t="s">
         <v>1783</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="42" t="s">
         <v>1859</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="76" t="s">
         <v>1772</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="42" t="s">
         <v>1859</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="76" t="s">
         <v>1784</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="42" t="s">
         <v>1859</v>
       </c>
     </row>
@@ -42431,13 +42090,13 @@
       <c r="A8" s="37" t="s">
         <v>1836</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="67">
         <v>9959.9550000000017</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="68">
         <v>18275.859999999997</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="69">
         <v>28235.814999999999</v>
       </c>
     </row>
@@ -42445,13 +42104,13 @@
       <c r="A9" s="38" t="s">
         <v>1837</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="70">
         <v>8789.7000000000007</v>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="71">
         <v>31033.880000000005</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="72">
         <v>39823.58</v>
       </c>
     </row>
@@ -42459,13 +42118,13 @@
       <c r="A10" s="38" t="s">
         <v>1838</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="70">
         <v>11501.494999999999</v>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="71">
         <v>19239.555</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="72">
         <v>30741.05</v>
       </c>
     </row>
@@ -42473,13 +42132,13 @@
       <c r="A11" s="41" t="s">
         <v>1815</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="73">
         <v>30251.15</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="74">
         <v>68549.295000000013</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="75">
         <v>98800.445000000007</v>
       </c>
     </row>
@@ -42506,10 +42165,10 @@
   </cols>
   <sheetData>
     <row r="9" spans="1:2">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="64" t="s">
         <v>1823</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="65" t="s">
         <v>1818</v>
       </c>
     </row>
@@ -42517,7 +42176,7 @@
       <c r="A10" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="68">
+      <c r="B10" s="36">
         <v>55284.087500000009</v>
       </c>
     </row>
@@ -42525,7 +42184,7 @@
       <c r="A11" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="69">
+      <c r="B11" s="40">
         <v>137464.86000000002</v>
       </c>
     </row>
@@ -42533,7 +42192,7 @@
       <c r="A12" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="69">
+      <c r="B12" s="40">
         <v>55334.36</v>
       </c>
     </row>
@@ -42541,7 +42200,7 @@
       <c r="A13" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="69">
+      <c r="B13" s="40">
         <v>34858.978000000003</v>
       </c>
     </row>
@@ -42549,7 +42208,7 @@
       <c r="A14" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="69">
+      <c r="B14" s="40">
         <v>53480.317499999983</v>
       </c>
     </row>
@@ -42557,7 +42216,7 @@
       <c r="A15" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="69">
+      <c r="B15" s="40">
         <v>78186.891000000003</v>
       </c>
     </row>
@@ -42565,7 +42224,7 @@
       <c r="A16" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="69">
+      <c r="B16" s="40">
         <v>51758.659999999996</v>
       </c>
     </row>
@@ -42573,15 +42232,15 @@
       <c r="A17" s="41" t="s">
         <v>1815</v>
       </c>
-      <c r="B17" s="70">
+      <c r="B17" s="42">
         <v>466368.15399999998</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="67" t="s">
+      <c r="A22" s="66" t="s">
         <v>1860</v>
       </c>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="66" t="s">
         <v>1861</v>
       </c>
     </row>
